--- a/Decks/Fractius.xlsx
+++ b/Decks/Fractius.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF76C370-8EB3-4AB3-9AF9-54603FE1DF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64A2616-2654-410D-99FB-12BC99B9BDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6CB2A5B-EF73-4B2F-9ACB-ADFB131847A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B6CB2A5B-EF73-4B2F-9ACB-ADFB131847A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fractius" sheetId="1" r:id="rId1"/>
@@ -392,13 +392,13 @@
     <t>Ash Barrens</t>
   </si>
   <si>
-    <t>Unlcaimed Territory</t>
-  </si>
-  <si>
     <t>Opulent Palace</t>
   </si>
   <si>
     <t>Blood Crypt</t>
+  </si>
+  <si>
+    <t>Unclaimed Territory</t>
   </si>
 </sst>
 </file>
@@ -886,7 +886,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>11</v>
@@ -1051,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/Fractius.xlsx
+++ b/Decks/Fractius.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64A2616-2654-410D-99FB-12BC99B9BDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6936968C-14AF-48A2-879E-9270599A78FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B6CB2A5B-EF73-4B2F-9ACB-ADFB131847A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6CB2A5B-EF73-4B2F-9ACB-ADFB131847A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fractius" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="120">
   <si>
     <t>Função</t>
   </si>
@@ -381,9 +381,6 @@
   </si>
   <si>
     <t>Fetch n WG WU</t>
-  </si>
-  <si>
-    <t>Plated Sliver</t>
   </si>
   <si>
     <t>Sandsteppe Citadel</t>
@@ -886,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>11</v>
@@ -1051,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>22</v>
@@ -1066,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>23</v>
@@ -1141,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1276,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>114</v>
@@ -1468,10 +1465,10 @@
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>45</v>

--- a/Decks/Fractius.xlsx
+++ b/Decks/Fractius.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6936968C-14AF-48A2-879E-9270599A78FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D460BA-EBFC-4B0F-AE88-FA2DA87C00AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6CB2A5B-EF73-4B2F-9ACB-ADFB131847A5}"/>
   </bookViews>
@@ -1060,10 +1060,10 @@
       </c>
       <c r="B17" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>23</v>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>24</v>
